--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_3857_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_3857_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Raf23278768bf42a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9f03e3ae20c14799"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,156 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>13/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_3857_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_3857_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9f03e3ae20c14799"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8d015a198305454b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,666 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.8900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.8900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
